--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-01T21:20:53.298Z</t>
+    <t>2026-10-02T15:09:01.956Z</t>
   </si>
   <si>
     <t>Financial Planning Advice and Financial Advisors | Ameriprise Financial</t>
